--- a/www/download/IND.gross_output.s.du.rpA1.xlsx
+++ b/www/download/IND.gross_output.s.du.rpA1.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>135346.794127923</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>138674.651668416</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>137756.696708215</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>136924.636158114</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>150852.800325318</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>148751.848403026</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>140437.838685402</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>150912.961258412</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>170365.630901712</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>209840.205883678</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>229741.493803493</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>244860.438384061</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>290767.179939016</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>337007.641186259</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>321235.013401396</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>72750.989858096</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>75303.769630641</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>69929.9413566128</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>71207.9999909288</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>74516.8092103247</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>79671.2991357086</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>78764.9397394051</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>78381.9930941735</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>87338.1960955246</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>99431.2248297228</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>105020.896441399</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>118665.279754615</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>138070.804406668</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>140884.954704075</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>112347.291441921</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>91829.6476482632</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>87354.8396230436</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>82592.3230017637</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>83520.9415205993</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>88432.1561500441</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>98057.6600162396</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>95229.8369107873</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>94292.7599812043</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>109529.654763045</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>128363.583296648</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>132349.069501655</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>149432.344471207</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>175848.846805934</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>227007.424609092</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>158846.439279632</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59973.1967203665</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>63564.7215523622</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>57495.402441934</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>54342.3802310273</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>52821.1319638649</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>50810.5889507893</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>47694.3746908131</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>47676.5559845817</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>52958.2408183957</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>62252.4222608911</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>68274.4150092057</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>75950.8352098986</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>88838.9426077123</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>98687.6840022625</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>92048.6721462758</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.235</t>
+          <t>1235317.38923719</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.226</t>
+          <t>1225856.39399621</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.213</t>
+          <t>1212622.98113336</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.177</t>
+          <t>1176756.88614017</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.255</t>
+          <t>1255487.70759697</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>1316946.9255461</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1249624.18883598</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.323</t>
+          <t>1323073.66118598</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1464591.55248734</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.697</t>
+          <t>1697205.62871096</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1.855</t>
+          <t>1855286.16965587</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.917</t>
+          <t>1916957.26121362</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2.192</t>
+          <t>2191631.72013757</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2.486</t>
+          <t>2486138.82110844</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.237</t>
+          <t>2237052.94129654</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>214366.317661045</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>219835.942353225</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>216428.926737525</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>217572.685291409</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>239729.95238146</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.269</t>
+          <t>268875.468505284</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>263578.372262187</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>259444.105719903</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>290593.940046456</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>350492.586477622</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>385709.460801132</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.416</t>
+          <t>416334.407157773</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>456066.544672759</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.511</t>
+          <t>511471.981623143</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.439</t>
+          <t>438623.052645043</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15.125</t>
+          <t>15125140.1996345</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>15.649</t>
+          <t>15648851.1551852</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>15.641</t>
+          <t>15640794.3230595</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>15.389</t>
+          <t>15389286.9940574</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>15.823</t>
+          <t>15822834.7441872</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>15.911</t>
+          <t>15911066.1894984</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>15.734</t>
+          <t>15734181.8260416</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>16.356</t>
+          <t>16355679.2244013</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>18.636</t>
+          <t>18635583.7985303</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>21.033</t>
+          <t>21033230.3461723</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>23.689</t>
+          <t>23688544.7797313</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>27.241</t>
+          <t>27240623.8784683</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>32.121</t>
+          <t>32120644.3093214</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>36.955</t>
+          <t>36954962.6092382</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>34.932</t>
+          <t>34931633.1262028</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4692.51441139427</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5167.11540117841</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4550.54739628026</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>4573.96433561059</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5199.87518398594</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5215.7581511497</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5609.66821965396</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5910.81431089521</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6608.28905354998</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6922.0857156953</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>6750.20578563156</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7267.64822276111</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7939.68932819797</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12186.5717174091</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>7513.67074112639</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>105407.83980991</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>108802.386233356</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>110591.809634107</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>105350.013974745</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>105319.124209512</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>103028.768792537</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>102830.951103749</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>106276.740920859</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>113925.803233739</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>128760.642712167</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>137811.896701498</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>155228.796372386</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>182475.503709806</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>195192.564190053</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>151089.54037742</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.669</t>
+          <t>669477.784842846</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.624</t>
+          <t>623572.245471605</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.588</t>
+          <t>588283.404474203</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.609</t>
+          <t>608987.943071866</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.639</t>
+          <t>639360.008295068</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.689</t>
+          <t>689160.495868173</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.639</t>
+          <t>639418.948964752</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.633</t>
+          <t>632681.827868585</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.726</t>
+          <t>726484.092843685</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.835</t>
+          <t>835221.184102429</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.884</t>
+          <t>883673.360546889</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0.981</t>
+          <t>980703.139999225</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>1.162</t>
+          <t>1162056.20559795</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1150336.24350536</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0.894</t>
+          <t>893575.486067054</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>55872.6584697202</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>55776.4113480025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>58282.7346124017</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>53199.4262843947</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>51938.4746663429</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>53660.1052629227</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>53501.7070487904</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>53548.6718959376</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>61206.2516470377</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>68989.9938540903</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>72168.8855039966</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>77228.8973164469</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>89248.1601772454</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>91364.3623306456</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>72325.4269987102</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>255245.227548478</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>257312.558496428</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>244490.385723489</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>259337.141284324</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>291385.637213891</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>320571.692479016</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>316076.800412482</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>339122.699462146</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>374428.312570841</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.433</t>
+          <t>433128.389511937</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.485</t>
+          <t>484776.252045111</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>529827.671494074</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.615</t>
+          <t>615252.347750168</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.639</t>
+          <t>639016.547773053</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.471</t>
+          <t>470958.044055318</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11147.7941336079</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10856.3321405091</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11256.2998013923</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11402.5019758811</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11012.2663861219</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12099.9940499436</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>12740.8715329426</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>13677.5499952646</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>15633.6505036692</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18360.1298910043</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18173.9781779504</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19523.240193442</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>20540.4396461186</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>21795.1539786279</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16519.9376664264</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>52289.898399789</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>51739.9280150896</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>50097.8629022633</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>53010.5879654596</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>58440.2305438274</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>59974.6857097518</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>55872.5372886151</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>56414.8165866922</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>63866.6065826262</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>72337.9539846026</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>79947.3559869621</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>87708.915051343</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>101020.609223991</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>104799.560392045</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>72368.4081409804</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>380412.452649353</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>374356.588402971</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>339367.363742591</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>350098.943683551</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>385658.327096052</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>407331.711030373</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>394174.796270456</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>389744.917204863</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>437011.570105362</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.497</t>
+          <t>496789.2473581</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>538494.94195788</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.572</t>
+          <t>571542.573665431</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.665</t>
+          <t>664624.182484453</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>682334.222379003</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.558</t>
+          <t>557738.808694323</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.402</t>
+          <t>402055.343816713</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>410112.760338004</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>391518.658465567</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>388079.405188408</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>399733.517567357</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.402</t>
+          <t>402110.965459282</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>383709.236977369</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>382552.989731255</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>416946.775153797</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.477</t>
+          <t>476805.645156546</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.521</t>
+          <t>520900.651026265</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>551277.699051974</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.624</t>
+          <t>624023.174608241</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.614</t>
+          <t>613557.426472199</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.513</t>
+          <t>513115.749195503</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>76456.6848538078</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>79144.7983101914</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>72429.9241747808</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>71708.330018348</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>74920.8191386037</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>82671.9795521984</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>76545.6301616945</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>78256.483868694</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>83958.9136066708</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>90559.1452732148</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>96935.4904917526</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>108747.485183836</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>123517.75084959</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>137606.25717866</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>117077.641291696</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>83192.409493203</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>82982.1976899486</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>78765.4896096467</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>79870.9379611927</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>89252.7716148755</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>90155.0072069377</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>85288.2265569414</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>86936.6220072088</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>93424.8515150232</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>97400.1909027568</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>102754.912882978</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>108184.044791722</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>125189.19068966</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>123313.137686832</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>102818.712297899</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.093</t>
+          <t>1092999.94026476</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.143</t>
+          <t>1142986.02570362</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.103</t>
+          <t>1103416.16618006</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1029612.6045958</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.219</t>
+          <t>1219047.65614973</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.313</t>
+          <t>1313035.8439106</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.308</t>
+          <t>1307687.28532044</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.424</t>
+          <t>1423602.25921686</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.588</t>
+          <t>1587926.14979748</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.733</t>
+          <t>1732606.97530745</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1.648</t>
+          <t>1647685.43300144</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1.667</t>
+          <t>1667348.66628731</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.963</t>
+          <t>1962587.10823928</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2220006.90914426</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2.181</t>
+          <t>2180736.4283481</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>9.305</t>
+          <t>9304699.01671316</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>9.517</t>
+          <t>9516949.22172793</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>9.605</t>
+          <t>9605090.35728528</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>9.492</t>
+          <t>9492475.80516174</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>9.607</t>
+          <t>9606585.64734557</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>10.196</t>
+          <t>10195908.491297</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10.265</t>
+          <t>10265243.6284606</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>10.268</t>
+          <t>10268028.6742771</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>11.905</t>
+          <t>11905393.5328367</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>13.397</t>
+          <t>13396785.2735971</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>14.644</t>
+          <t>14644133.4357906</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>15.509</t>
+          <t>15509335.3394291</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>17.102</t>
+          <t>17101798.8856858</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>18.798</t>
+          <t>18798373.4257834</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>17.932</t>
+          <t>17931611.1463697</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>34660.4995733866</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>35732.5062632677</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>34605.1945184509</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>34139.521326525</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39064.7107171662</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42361.1698085142</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42112.9735874373</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>40734.0642951319</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>46726.0106925223</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>56472.9594669442</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>63604.7868911541</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>69407.8210992127</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>82057.5273426512</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>79182.9172922224</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>64976.0926573768</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.459</t>
+          <t>459194.499393399</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>460417.546853132</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>433998.097019396</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>446144.808198018</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>470455.747515912</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0.505</t>
+          <t>504864.708347997</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.489</t>
+          <t>489143.359027463</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.496</t>
+          <t>496117.119664675</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>555959.967744375</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.639</t>
+          <t>639101.775009547</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0.676</t>
+          <t>676368.09187755</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>759745.377851323</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.866</t>
+          <t>866234.079668841</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>0.853</t>
+          <t>852533.672077268</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>0.645</t>
+          <t>645013.260764447</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1.592</t>
+          <t>1592351.08890111</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>1528914.08145294</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>1461866.07262078</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1.312</t>
+          <t>1312311.57123305</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.393</t>
+          <t>1393293.89474217</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.494</t>
+          <t>1493820.66080674</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.398</t>
+          <t>1397609.06178528</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.361</t>
+          <t>1361075.65543118</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1.519</t>
+          <t>1518716.01550664</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1.757</t>
+          <t>1756773.68626803</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1.883</t>
+          <t>1883310.61411118</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2.027</t>
+          <t>2026635.95676085</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2.268</t>
+          <t>2268273.04923961</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2609894.62742979</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2.054</t>
+          <t>2053821.75802714</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.645</t>
+          <t>644980.071881021</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.652</t>
+          <t>651859.518766038</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>636020.870106034</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.539</t>
+          <t>538957.752690119</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.608</t>
+          <t>608486.888497189</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.669</t>
+          <t>669344.649559848</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.634</t>
+          <t>633564.85441936</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>659842.106012385</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.733</t>
+          <t>732865.99845117</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0.873</t>
+          <t>872798.716064598</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.936</t>
+          <t>935619.401444167</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1.028</t>
+          <t>1028146.2919226</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>1.165</t>
+          <t>1165240.8079673</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>1.328</t>
+          <t>1328219.49377959</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1.136</t>
+          <t>1135874.11336898</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>25298.2225663757</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>24856.9460287351</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22235.0778035833</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23591.2249353207</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23282.3559571053</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>24189.9922609851</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23118.0726520964</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23950.8249876448</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>26679.7121047822</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>27915.2861371036</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31477.3450374465</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>32601.3092444161</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37568.9718171686</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>43727.0548562602</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>34990.9427160823</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3757.90976026051</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3363.04071730176</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3137.24969311551</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3366.55083574022</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3307.43509041312</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3684.57019850205</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3451.58124388945</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3543.5680206026</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4360.9084469755</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>5424.06075259038</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>5904.14214782049</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>6424.31802211184</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7227.97827031583</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8219.4515774409</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>7028.55871097478</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12017.2680738665</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11823.0554841472</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11874.7755587986</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12033.6095478498</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>11974.1329827488</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10882.4905096906</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10514.6431383898</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>10699.9235603837</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12489.6941173067</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>14895.3872609991</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>16538.7768191197</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18647.2147808172</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>23515.8523016654</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>23358.2851625982</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>15742.9308635315</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>538197.980869479</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.569</t>
+          <t>569090.034374101</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>558946.709000887</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.589</t>
+          <t>588549.781946811</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.638</t>
+          <t>637877.056175451</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.675</t>
+          <t>674980.698318909</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.672</t>
+          <t>671712.185343213</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>679637.430164617</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.746</t>
+          <t>746265.639305788</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.863</t>
+          <t>862621.104917358</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.933</t>
+          <t>933431.143739185</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>979650.024427354</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1.095</t>
+          <t>1095106.55029724</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1.295</t>
+          <t>1294502.08912734</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.173</t>
+          <t>1172794.94213155</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2396.95840748512</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2402.38684390733</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2068.50455644335</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2205.58449714554</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2585.16705991234</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2964.6893873484</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2389.98481922322</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2554.86976609148</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2779.97469998576</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2906.41082307424</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2919.27018269207</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3392.48887754912</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3852.40066944359</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4343.42873804133</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3532.65490211093</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>171849.445139216</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>175970.3855498</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>162241.471115245</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>177885.713291879</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>196020.593320885</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>196987.100205587</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>197623.764857959</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>171022.234120717</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>224188.868966319</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>252076.395636156</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>279343.964342066</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>292013.255832627</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.348</t>
+          <t>348003.364766351</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.391</t>
+          <t>391076.587081626</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>316563.711921944</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>296032.085006988</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>304179.058969324</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>295339.373473486</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>293086.507197674</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>291375.314587542</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>301253.689643302</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>256136.191060093</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>246467.854501997</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>264122.710941678</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>299665.386683302</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>330627.952386626</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.361</t>
+          <t>361432.656777559</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>437225.300901855</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.478</t>
+          <t>478053.014546</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.402</t>
+          <t>401819.935185989</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>96298.5692039991</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>95972.3348988758</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>90060.0355781298</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>94019.0618782216</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>97481.7815271282</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>105889.755460495</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>103113.723525943</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>102802.791205317</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>109069.736250402</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>122689.73341897</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>126439.137909294</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>132181.568668609</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>153922.051315418</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>172266.768655045</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>129655.902787787</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>216551.583481949</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>229332.067848013</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.203</t>
+          <t>202655.326774062</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>185136.995100998</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>239039.382481768</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>234067.926224987</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>225649.323934757</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>199701.389913337</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>211476.44357918</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>223259.58773338</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>234804.664372058</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>245547.528938426</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>282460.128114298</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.314</t>
+          <t>314051.75069194</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>278657.144173163</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1.438</t>
+          <t>1437647.33748264</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>1456667.26065859</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.359</t>
+          <t>1358543.41924397</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1.274</t>
+          <t>1274211.10396255</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.236</t>
+          <t>1235544.17994714</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1.297</t>
+          <t>1296520.78620272</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1.294</t>
+          <t>1293917.25343366</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1284686.11674923</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>1.388</t>
+          <t>1388163.08868063</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1510348.2113757</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1.616</t>
+          <t>1616318.31980876</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1.657</t>
+          <t>1657113.2578281</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>1.956</t>
+          <t>1955743.95465118</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2.184</t>
+          <t>2184474.60074306</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1.995</t>
+          <t>1994623.2760493</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>42332.0268304509</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>43631.4728915138</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>39811.9809889185</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>38602.9395194375</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38278.0174614749</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>38173.0956758626</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>37544.1562649694</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>36979.0439903642</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>41280.9281280442</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>46284.0424175082</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>51690.6558459999</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>57663.4248217027</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>72780.7421582093</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>81900.1856716505</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>71975.3388486814</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19923.0942575188</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19475.4298334753</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18028.6870036442</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>18150.9394333477</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>18943.1106707166</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19888.9719436474</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>19434.6925557942</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>19701.9708144501</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>22397.9092573291</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>24430.2500387334</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>25880.9691632086</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>28071.2517504607</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>33146.0909334973</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>39323.3313480368</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>31241.4998055331</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>76914.6265402545</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>75146.5877024326</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>71958.2408309707</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>74393.7038292108</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>79064.0247918589</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>85614.6316752692</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>78880.7456702743</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>78667.09747747</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>88338.5949040121</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>100904.578329726</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>110859.418137008</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>117728.821226885</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>139791.330355757</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>139735.284235306</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>108623.779126572</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.424</t>
+          <t>423711.634011283</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.436</t>
+          <t>436048.632750536</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>443704.141600282</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>436515.504665376</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>463961.592286364</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.474</t>
+          <t>474139.893898094</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>444019.241439273</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.455</t>
+          <t>455395.28282776</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.505</t>
+          <t>505423.548719403</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.584</t>
+          <t>584434.947789817</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.627</t>
+          <t>626969.315978242</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0.643</t>
+          <t>643331.601435453</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0.718</t>
+          <t>718241.292991551</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>849756.02327391</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0.696</t>
+          <t>696182.622594697</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>274026.187858561</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.269</t>
+          <t>268867.76866624</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>260930.259815024</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>251764.348497001</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>262348.698572258</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>288721.917794981</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>253186.308664362</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>272531.725457419</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>307117.919099833</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.378</t>
+          <t>377747.363251336</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.391</t>
+          <t>391317.669688746</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>419854.285699805</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.474</t>
+          <t>474483.636621961</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>529546.088937987</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.405</t>
+          <t>405174.505123604</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2.075</t>
+          <t>2075477.16879347</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2.102</t>
+          <t>2102229.26078075</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2.116</t>
+          <t>2115898.24444565</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2.135</t>
+          <t>2134900.09133817</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2.294</t>
+          <t>2294470.95693763</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2.478</t>
+          <t>2477783.55153935</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2.296</t>
+          <t>2295992.27673124</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2.256</t>
+          <t>2255892.35778039</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2.465</t>
+          <t>2465366.0399651</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2.871</t>
+          <t>2870529.83590764</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>3.176</t>
+          <t>3175960.9726989</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>3.408</t>
+          <t>3407584.38251061</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>3.725</t>
+          <t>3725123.60574935</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>4.089</t>
+          <t>4089457.73268862</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>3.195</t>
+          <t>3194631.24709005</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>17.31</t>
+          <t>17310016.1783729</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>17.881</t>
+          <t>17881209.629737</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>18.299</t>
+          <t>18298864.9691078</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>18.483</t>
+          <t>18483400.9900094</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>19.277</t>
+          <t>19277011.1355627</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>20.262</t>
+          <t>20262121.4736135</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>20.415</t>
+          <t>20415399.9136647</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>21.716</t>
+          <t>21715558.8297831</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>24.238</t>
+          <t>24237726.3442001</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>27.537</t>
+          <t>27536961.6993045</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>30.307</t>
+          <t>30307114.1812607</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>33.105</t>
+          <t>33105193.903554</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>37.265</t>
+          <t>37265366.5815706</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>41.73</t>
+          <t>41729815.9122408</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>40.016</t>
+          <t>40015945.5745828</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>55.182</t>
+          <t>55182308.5366997</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>56.556</t>
+          <t>56556389.0503581</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>56.599</t>
+          <t>56598550.2992956</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>56.061</t>
+          <t>56060688.4328249</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>58.306</t>
+          <t>58306395.8341117</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>60.817</t>
+          <t>60817361.9019018</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>60.203</t>
+          <t>60202725.9733039</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>62.264</t>
+          <t>62263778.5854962</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>70.209</t>
+          <t>70209291.8668545</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>79.624</t>
+          <t>79623724.2735859</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>87.526</t>
+          <t>87525633.878685</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>95.929</t>
+          <t>95929115.303749</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>109.398</t>
+          <t>109397506.893586</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>122.789</t>
+          <t>122789481.799158</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>114.158</t>
+          <t>114158105.32809</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>gross_output.s.du</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA1</t>
